--- a/finegray/demo/finegray_results.xlsx
+++ b/finegray/demo/finegray_results.xlsx
@@ -392,7 +392,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="12">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -402,51 +402,27 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
-      <b/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
       <b/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
+      <sz val="12"/>
       <name val="Arial"/>
     </font>
     <font>
+      <i/>
       <sz val="10"/>
-      <name val="Arial"/>
-      <i/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <i/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
+      <i/>
       <sz val="8"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <i/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <i/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -460,10 +436,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEDF2F9"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -473,457 +450,280 @@
     </border>
     <border/>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="none"/>
-      <top style="none"/>
+      <right style="thin"/>
+      <top/>
       <bottom style="thin"/>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="top" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="top" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -946,22 +746,22 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="16" t="s">
         <v>1</v>
       </c>
     </row>
@@ -969,19 +769,19 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="15" t="s">
         <v>29</v>
       </c>
     </row>
@@ -989,19 +789,19 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="21" t="s">
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1009,19 +809,19 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="11" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1029,19 +829,19 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="7" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1049,19 +849,19 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="32" t="s">
+      <c r="C6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1069,19 +869,19 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="32" t="s">
+      <c r="F7" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1089,19 +889,19 @@
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="32" t="s">
+      <c r="F8" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1109,19 +909,19 @@
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="34" t="s">
+      <c r="D9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="34" t="s">
+      <c r="E9" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="33" t="s">
+      <c r="F9" s="9" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1156,46 +956,46 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="3" t="s">
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="16" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1203,43 +1003,43 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="12" t="s">
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="12" t="s">
+      <c r="D2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="12" t="s">
+      <c r="G2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="J2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="12" t="s">
+      <c r="J2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="M2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="N2" s="27" t="s">
+      <c r="M2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" s="19" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1247,43 +1047,43 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="52" t="s">
+      <c r="B3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="52" t="s">
+      <c r="F3" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="52" t="s">
+      <c r="G3" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="H3" s="53" t="s">
+      <c r="H3" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="52" t="s">
+      <c r="I3" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="52" t="s">
+      <c r="J3" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="K3" s="53" t="s">
+      <c r="K3" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="52" t="s">
+      <c r="L3" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="M3" s="52" t="s">
+      <c r="M3" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="53" t="s">
+      <c r="N3" s="34" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1291,43 +1091,43 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="70" t="s">
+      <c r="E4" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="43" t="s">
+      <c r="F4" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="43" t="s">
+      <c r="G4" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="H4" s="70" t="s">
+      <c r="H4" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="I4" s="43" t="s">
+      <c r="I4" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="43" t="s">
+      <c r="J4" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="K4" s="70" t="s">
+      <c r="K4" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="L4" s="43" t="s">
+      <c r="L4" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="M4" s="43" t="s">
+      <c r="M4" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="N4" s="70" t="s">
+      <c r="N4" s="23" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1335,43 +1135,43 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="C5" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="43" t="s">
+      <c r="D5" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="70" t="s">
+      <c r="E5" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="43" t="s">
+      <c r="F5" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="43" t="s">
+      <c r="G5" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="70" t="s">
+      <c r="H5" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="43" t="s">
+      <c r="I5" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="J5" s="43" t="s">
+      <c r="J5" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="K5" s="70" t="s">
+      <c r="K5" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="L5" s="43" t="s">
+      <c r="L5" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="M5" s="43" t="s">
+      <c r="M5" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="N5" s="70" t="s">
+      <c r="N5" s="23" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1379,43 +1179,43 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="61" t="s">
+      <c r="B6" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="M6" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="N6" s="70" t="s">
+      <c r="C6" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="M6" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="N6" s="23" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1423,43 +1223,43 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="61" t="s">
+      <c r="B7" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="71" t="s">
+      <c r="C7" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="71" t="s">
+      <c r="D7" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="71" t="s">
+      <c r="G7" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="J7" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="M7" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="N7" s="70" t="s">
+      <c r="J7" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="M7" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="N7" s="23" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1467,43 +1267,43 @@
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="61" t="s">
+      <c r="B8" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="43" t="s">
+      <c r="C8" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="43" t="s">
+      <c r="D8" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="70" t="s">
+      <c r="E8" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="43" t="s">
+      <c r="F8" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="43" t="s">
+      <c r="G8" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="70" t="s">
+      <c r="H8" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="43" t="s">
+      <c r="I8" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="43" t="s">
+      <c r="J8" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="K8" s="70" t="s">
+      <c r="K8" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="L8" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="M8" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="N8" s="70" t="s">
+      <c r="L8" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="M8" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="N8" s="23" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1511,43 +1311,43 @@
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="63" t="s">
+      <c r="B9" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="67" t="s">
+      <c r="C9" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="67" t="s">
+      <c r="D9" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" s="67" t="s">
+      <c r="G9" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="J9" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="67" t="s">
+      <c r="J9" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="M9" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="N9" s="72" t="s">
+      <c r="M9" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="N9" s="27" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1555,43 +1355,43 @@
       <c r="A10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="62" t="s">
+      <c r="B10" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="69" t="s">
+      <c r="C10" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="68" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="73" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="69" t="s">
+      <c r="D10" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="G10" s="68" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="73" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="69" t="s">
+      <c r="G10" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="J10" s="68" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="73" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" s="69" t="s">
+      <c r="J10" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="M10" s="68" t="s">
-        <v>1</v>
-      </c>
-      <c r="N10" s="73" t="s">
+      <c r="M10" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="N10" s="25" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1630,172 +1430,172 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="77" t="s">
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="79" t="s">
+      <c r="A2" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="47" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="79" t="s">
+      <c r="C2" s="45" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="79" t="s">
+      <c r="D2" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="79" t="s">
+      <c r="E2" s="46" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="76" t="s">
+      <c r="A3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="40" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="82" t="s">
+      <c r="A4" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="83" t="s">
+      <c r="C4" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="83" t="s">
+      <c r="D4" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="83" t="s">
+      <c r="E4" s="42" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="76" t="s">
+      <c r="A5" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="40" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="82" t="s">
+      <c r="A6" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="83" t="s">
+      <c r="C6" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="D6" s="83" t="s">
+      <c r="D6" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="E6" s="83" t="s">
+      <c r="E6" s="42" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="76" t="s">
+      <c r="A7" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="40" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="82" t="s">
+      <c r="A8" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="37" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="83" t="s">
+      <c r="C8" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="83" t="s">
+      <c r="D8" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="83" t="s">
+      <c r="E8" s="42" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="76" t="s">
+      <c r="A9" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="40" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="84" t="s">
+      <c r="A10" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="C10" s="85" t="s">
+      <c r="C10" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="D10" s="85" t="s">
+      <c r="D10" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="E10" s="85" t="s">
+      <c r="E10" s="44" t="s">
         <v>91</v>
       </c>
     </row>
@@ -1818,86 +1618,86 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="77" t="s">
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="79" t="s">
+      <c r="A2" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="79" t="s">
+      <c r="C2" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="D2" s="79" t="s">
+      <c r="D2" s="46" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="76" t="s">
+      <c r="A3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="40" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="76" t="s">
+      <c r="A4" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="40" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="80" t="s">
+      <c r="A5" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="49" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="81" t="s">
+      <c r="C5" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="D5" s="81" t="s">
+      <c r="D5" s="51" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="88" t="s">
+      <c r="A6" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="88" t="s">
+      <c r="C6" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="48" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1923,162 +1723,162 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="65" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="77" t="s">
+      <c r="B1" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="65" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="79" t="s">
+      <c r="A2" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="64" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="79" t="s">
+      <c r="C2" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="79" t="s">
+      <c r="D2" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="E2" s="79" t="s">
+      <c r="E2" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="F2" s="79" t="s">
+      <c r="F2" s="63" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="76" t="s">
+      <c r="A3" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="53" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="56" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="57" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="82" t="s">
+      <c r="A4" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="83" t="s">
+      <c r="C4" s="58" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="83" t="s">
+      <c r="D4" s="58" t="s">
         <v>108</v>
       </c>
-      <c r="E4" s="83" t="s">
+      <c r="E4" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="F4" s="83" t="s">
+      <c r="F4" s="59" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="76" t="s">
+      <c r="A5" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="53" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="57" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="82" t="s">
+      <c r="A6" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="83" t="s">
+      <c r="C6" s="58" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="83" t="s">
+      <c r="D6" s="58" t="s">
         <v>110</v>
       </c>
-      <c r="E6" s="83" t="s">
+      <c r="E6" s="58" t="s">
         <v>113</v>
       </c>
-      <c r="F6" s="83" t="s">
+      <c r="F6" s="59" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="76" t="s">
+      <c r="A7" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="53" t="s">
         <v>104</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="56" t="s">
         <v>116</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="57" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="84" t="s">
+      <c r="A8" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="C8" s="85" t="s">
+      <c r="C8" s="60" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="85" t="s">
+      <c r="D8" s="60" t="s">
         <v>112</v>
       </c>
-      <c r="E8" s="85" t="s">
+      <c r="E8" s="60" t="s">
         <v>117</v>
       </c>
-      <c r="F8" s="85" t="s">
+      <c r="F8" s="61" t="s">
         <v>122</v>
       </c>
     </row>
